--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2955ADE4-AE83-49DB-BDBF-851BE6591CDB}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD805813-4E07-40B2-8E5C-BC5488B041BC}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
+    <workbookView xWindow="-19320" yWindow="-60" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
     <sheet name="Mechanism" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
   <si>
     <t>Paper</t>
   </si>
@@ -87,15 +88,9 @@
     <t>1) invading sargassum have lower genetic diversity than native populations</t>
   </si>
   <si>
-    <t>The paper has little to no evidence, no direct empirical work testing hypothesized mechanism is presented or cited, if a mechanisms is suggested the mechanism is purely conjecture/hypothesis with no or little data in the manuscript or in other papers supporting the conjecture/hypothesis.  No demographic work.</t>
-  </si>
-  <si>
     <t>The paper has some evidence, some empirical work testing hypothesized mechanism is presented or cited but is correlary with little to no alternative mechanisms tested, the suggeset mechanisms is a more data driven hypothesis. No demographic work.</t>
   </si>
   <si>
-    <t>The paper has strong evidence, empirical work testing hypothesized mechanism is presented or cited and is expreimentally obtained, observational evidence includes models with drivers and response data that were apriori selected,alternative mechanisms have also been evaluated and ruled out, the suggeset mechanisms is very likely mechanism. Evidence can be demographically tied.</t>
-  </si>
-  <si>
     <t>Changes in Population of Exotic Rainbow Smelt in Lake Superior: Boom to Bust, 1974-2005</t>
   </si>
   <si>
@@ -123,9 +118,6 @@
     <t>2) the summer upwelling has weakened during the summer, and increased thermal stress on other heat-senstive seaweeds in 2006. The decline in sargassum correlates with the beginning of the weakening of the summer upwelling. But, sargassum are considered thermal tolerant during this period because it coincides with their dormant phase.</t>
   </si>
   <si>
-    <t>Intermediate to Strong</t>
-  </si>
-  <si>
     <t>Weak</t>
   </si>
   <si>
@@ -165,9 +157,6 @@
     <t>Bilio &amp; Niermann</t>
   </si>
   <si>
-    <t>Poor to Intermediate</t>
-  </si>
-  <si>
     <t>2) Declines in M. leidyi correlate with the subsequent invasion B. ovata, and the process of B. ovata controlling jellies was consistent with how they control jellies in their native range.</t>
   </si>
   <si>
@@ -183,15 +172,191 @@
     <t>Dexter et al</t>
   </si>
   <si>
-    <t>The paper  has evidence, empirical work testing hypothesized mechanism is presented or cited but is mostely correlary alternative mechanisms have also been evaluated and ruled out, may have some post hoc modelling with suggested mechansims. Some demographic work. The mechanism is presented is likely</t>
+    <t>Poor</t>
+  </si>
+  <si>
+    <t>1) B. Coregoni was detected from one individual in 2006, grew to a peak abundance of 247 individuals/ m 3 then rapidly declined in 2011. Yearly timing of the peak abundance through the time period was highly variable.</t>
+  </si>
+  <si>
+    <t>2)  P. forbesi was consistently abundant at 3558/ cubic meter had a peak in 2010 of 10,725 per cubic meter and small number in 2013 per cubic meter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3) most peaks in abundance occurred in the autumn when temperatures are high and chlorophyll conditions are low. </t>
+  </si>
+  <si>
+    <t>4) postive correlation with chloriphyll a concentrations and peak abundance of B. coregoni, but a negative correlation with chloraphyll a concentrations and peak abundance of P. forbesi.</t>
+  </si>
+  <si>
+    <t>5) the timing of a previous invasive species P. inopinus that went extinct (narrative) was consistent with the establishment of P. forbesi.</t>
+  </si>
+  <si>
+    <t>6) B coregoni has a native congener B. longirostris.</t>
+  </si>
+  <si>
+    <t>Severe and rapid population declines in exotic birds</t>
+  </si>
+  <si>
+    <t>Aagaard &amp; Lockwood</t>
+  </si>
+  <si>
+    <t>Boom-Bust (all categories)</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>1) No evaluation of the potential mechanisms were made, the goal of the paper was to describe declines in non-native birds.</t>
+  </si>
+  <si>
+    <t>Trophic cascades triggered by overfishing reveal possible mechanisms of ecosystem regime shifts</t>
+  </si>
+  <si>
+    <t>Daskalov et al</t>
+  </si>
+  <si>
+    <t>1) no evaluation of the potential mechanisms were made, the goal of the paper was to assess trophic cascades and ecosystem regime shifts</t>
+  </si>
+  <si>
+    <t>Invasion impacts and dynamics of a European-wide introduced species</t>
+  </si>
+  <si>
+    <t>Huabrock et al</t>
+  </si>
+  <si>
+    <t>1) No evaluation of the potential mechanisms were made, the goal of the paper was to describe a new cumulative abundance curve and its potential for predicting a species impacts</t>
+  </si>
+  <si>
+    <t>2) latittude and runooff depth had negative and postive relationship, respectivly, to the rate of change of abundance which might inform boom-bust</t>
+  </si>
+  <si>
+    <t>3) decreasing water temperature and depths, and increasing competive interactions combined to drive declines in P. antipodarum population decline in another study that was cited</t>
+  </si>
+  <si>
+    <t>The contribution of cold winter temperatures to the 2003 alewife population collapse in Lake Huron</t>
+  </si>
+  <si>
+    <t>Dunlop &amp; Riley</t>
+  </si>
+  <si>
+    <t>1) Alewife are the primary prey of chinook salmon, and Alewife were in decline</t>
+  </si>
+  <si>
+    <t>2) GAM model results showed that at high chinook salmon abundance the relationship between chinook salmon and alewife abundance is negative</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Sargassum muticum</t>
+  </si>
+  <si>
+    <t>Osmerus mordax</t>
+  </si>
+  <si>
+    <t>Faxonius rusticus</t>
+  </si>
+  <si>
+    <t>Mnemiopsis leidyi</t>
+  </si>
+  <si>
+    <t>Pseudodiaptomus forbesi</t>
+  </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>Aurelia aurita</t>
+  </si>
+  <si>
+    <t>Potamopyrgus antipodarum</t>
+  </si>
+  <si>
+    <t>Oncorhnchus tshawytscha</t>
+  </si>
+  <si>
+    <t>Stong*</t>
+  </si>
+  <si>
+    <t>Intermediate*</t>
+  </si>
+  <si>
+    <t>Per Capita Effects of Non-native Mayan Cichlids (Cichlasoma urophthalmus; Gunther) on Native Fish in Estuarine Southern Everglades</t>
+  </si>
+  <si>
+    <t>Harrison et al</t>
+  </si>
+  <si>
+    <t>Mayaheros urophthalmus</t>
+  </si>
+  <si>
+    <t>Unfavorable environmental conditions</t>
+  </si>
+  <si>
+    <t>1) After cold fronts, most sites saw declines in mayan cichlid numbers, the rest of the discussion and results were about the impacts of mayan cichlids on native communities.</t>
+  </si>
+  <si>
+    <t>The paper has little to no evidence, no direct empirical work testing hypothesized mechanism is presented or cited, if a mechanisms is suggested the mechanism is purely conjecture/hypothesis with no or little data in the manuscript or cited in discussion supporting the conjecture/hypothesis.  No demographic work.</t>
+  </si>
+  <si>
+    <t>The paper has strong evidence, empirical work testing hypothesized mechanism is presented or cited and is expreimentally obtained, observational evidence includes models with drivers and response data that were apriori selected,alternative mechanisms have also been evaluated and ruled out, the suggested mechanisms is very likely the mechanism. Evidence can be demographically tied.</t>
+  </si>
+  <si>
+    <t>The paper  has evidence, empirical work testing hypothesized mechanism is presented or cited but is mostely correlary alternative mechanisms have also been evaluated and ruled out, may have some post hoc modelling with suggested mechansims. The mechanism presented is likely. Mechanism is not demographically tied.</t>
+  </si>
+  <si>
+    <t>Boom means bust: interactons between El Nino Southern Oscillation (ENSO), rainfall and the processes threatening mammal species in arid australia</t>
+  </si>
+  <si>
+    <t>Letnic &amp; Dickman</t>
+  </si>
+  <si>
+    <t>Felis catus</t>
+  </si>
+  <si>
+    <t>1) Abunances of cats increase 1-2 years after heavy rainfall years which coincides with large increases in small mammal abundance's</t>
+  </si>
+  <si>
+    <t>Resource matching from pulsed resource event</t>
+  </si>
+  <si>
+    <t>The Budgerigar in Florida: Rise and Fall of an Exotic Psittacid</t>
+  </si>
+  <si>
+    <t>Pranty</t>
+  </si>
+  <si>
+    <t>Melopsittacus undulatus</t>
+  </si>
+  <si>
+    <t>Boom-bust</t>
+  </si>
+  <si>
+    <t>1) Four extremely severe cold fronts occurred in 1977, 1983, 1986 and 1989, but there were no declines in abundance after the 3 of the 4 freezes, Cold alone is not a common driver of bird mortality, but lack of food from sudden freezes and snow cover are more common. the native habitat in australia udergos cold front of similar magnitude so they should be relatively resistant to the cold</t>
+  </si>
+  <si>
+    <t>2) House sparrows compete with the Budgerigars for nesting boxes and  Humans provided nesting boxes for which budgerigars used a lot of. Redevelopment from retirement communities to commercial could reduce the numbers of nesting boxes. Author thought this was the most likely cause</t>
+  </si>
+  <si>
+    <t>3) Little evidence for disease</t>
+  </si>
+  <si>
+    <t>Poor*</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -207,7 +372,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -226,22 +391,52 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -257,6 +452,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -604,7 +803,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="58.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -612,7 +811,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>48</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -620,7 +819,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -630,252 +829,597 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF18FAA-193E-4ADD-BAC0-7E416D9C0956}">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="64.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="4" max="4" width="24.109375" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="18.77734375" customWidth="1"/>
+    <col min="7" max="7" width="64.109375" customWidth="1"/>
     <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="57.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="5"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="1" t="s">
+      <c r="C9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="F22" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="F24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="G27" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="1" t="s">
+      <c r="E29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="10" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="G29" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="10" t="s">
         <v>14</v>
       </c>
+      <c r="E30" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="8"/>
+      <c r="B34" s="10"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="48">
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
     <mergeCell ref="E9:E12"/>
     <mergeCell ref="D9:D12"/>
     <mergeCell ref="C9:C12"/>
     <mergeCell ref="B9:B12"/>
     <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD805813-4E07-40B2-8E5C-BC5488B041BC}"/>
+  <xr:revisionPtr revIDLastSave="457" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAB55474-0266-4454-828D-26802BD9B0BC}"/>
   <bookViews>
     <workbookView xWindow="-19320" yWindow="-60" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
@@ -17,7 +17,6 @@
     <sheet name="Mechanism" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="119">
   <si>
     <t>Paper</t>
   </si>
@@ -289,9 +288,6 @@
     <t>Mayaheros urophthalmus</t>
   </si>
   <si>
-    <t>Unfavorable environmental conditions</t>
-  </si>
-  <si>
     <t>1) After cold fronts, most sites saw declines in mayan cichlid numbers, the rest of the discussion and results were about the impacts of mayan cichlids on native communities.</t>
   </si>
   <si>
@@ -316,9 +312,6 @@
     <t>1) Abunances of cats increase 1-2 years after heavy rainfall years which coincides with large increases in small mammal abundance's</t>
   </si>
   <si>
-    <t>Resource matching from pulsed resource event</t>
-  </si>
-  <si>
     <t>The Budgerigar in Florida: Rise and Fall of an Exotic Psittacid</t>
   </si>
   <si>
@@ -328,9 +321,6 @@
     <t>Melopsittacus undulatus</t>
   </si>
   <si>
-    <t>Boom-bust</t>
-  </si>
-  <si>
     <t>1) Four extremely severe cold fronts occurred in 1977, 1983, 1986 and 1989, but there were no declines in abundance after the 3 of the 4 freezes, Cold alone is not a common driver of bird mortality, but lack of food from sudden freezes and snow cover are more common. the native habitat in australia udergos cold front of similar magnitude so they should be relatively resistant to the cold</t>
   </si>
   <si>
@@ -341,6 +331,69 @@
   </si>
   <si>
     <t>Poor*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morris et al. </t>
+  </si>
+  <si>
+    <t>Using long-term datasets to study exotic plant invasions on rangelands in the western United States</t>
+  </si>
+  <si>
+    <t>Salsola tragus</t>
+  </si>
+  <si>
+    <t>1)It was inferred that since Lehmann lovegrass was shown to increase due to above average rainfall and then a subsequent drought that this was a similar mechanism for this species.</t>
+  </si>
+  <si>
+    <t>Environmental thresholds for pulsed resources</t>
+  </si>
+  <si>
+    <t>Contrasting invasion histories and effects of three non-native fishes observed with long-term monitoring data</t>
+  </si>
+  <si>
+    <t>Pintar et al.</t>
+  </si>
+  <si>
+    <t>Hemichromis letourneuxi</t>
+  </si>
+  <si>
+    <t>1) Cold water and drought events preceeded the boom-bust, and large non-native fishes experienced declines during those cold water conditions</t>
+  </si>
+  <si>
+    <t>2) Paper was more focused on impacts that non-natives have on native species</t>
+  </si>
+  <si>
+    <t>Environmental thresholds for ambient abiotic conditions</t>
+  </si>
+  <si>
+    <t>The Rise and Fall of a Reindeer Herd</t>
+  </si>
+  <si>
+    <t>Scheffer</t>
+  </si>
+  <si>
+    <t>Rangifer tarandus</t>
+  </si>
+  <si>
+    <t>1) There are no predators large enough to hunt reindeer in the islans</t>
+  </si>
+  <si>
+    <t>2) From behavioral observations and food preference experiments, taller shrub-like lichens are a key winter foods supply for the reindeer, a combination of cold winters that crusted ice inhibiting reindeer to access the lichens and large numbers that depleted the lichens, die offs were seen during the winter.</t>
+  </si>
+  <si>
+    <t>3) a small lack of sampling, corresponded with a period of military occupation, so poaching could have happened but the decline in popualtion size was already underway.</t>
+  </si>
+  <si>
+    <t>4) Disease and inbreeding were mentioned and ruled out, but with little rationale</t>
+  </si>
+  <si>
+    <t>Extreme Overshoot Of Resource Carrying Capacity</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>5) Question was why didn't St. George Island have a similar trend though the islands were of similar size</t>
   </si>
 </sst>
 </file>
@@ -414,18 +467,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -436,6 +477,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -811,7 +864,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -819,7 +872,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +882,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF18FAA-193E-4ADD-BAC0-7E416D9C0956}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" customWidth="1"/>
@@ -838,7 +891,7 @@
     <col min="4" max="4" width="24.109375" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="64.109375" customWidth="1"/>
+    <col min="7" max="7" width="67.6640625" customWidth="1"/>
     <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="57.77734375" customWidth="1"/>
   </cols>
@@ -867,22 +920,22 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G2" t="s">
@@ -890,33 +943,33 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="8" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -924,66 +977,66 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="5"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
       <c r="G6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="A7" s="8"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
       <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
       <c r="G8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="10" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -991,55 +1044,55 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="5"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="10"/>
       <c r="G10" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="4"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="10"/>
       <c r="G11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="5"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="4"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1047,44 +1100,44 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="10"/>
       <c r="G14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="4"/>
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="10"/>
       <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1092,56 +1145,56 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="4"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="10"/>
       <c r="G17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="4"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="4"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="10"/>
       <c r="G19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="4"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="4"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="10"/>
       <c r="G21" s="1" t="s">
         <v>50</v>
       </c>
@@ -1153,16 +1206,16 @@
       <c r="B22" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="10" t="s">
+      <c r="F22" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -1173,19 +1226,19 @@
       <c r="A23" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="6" t="s">
         <v>54</v>
       </c>
       <c r="G23" s="1" t="s">
@@ -1193,22 +1246,22 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="10" t="s">
         <v>44</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -1216,44 +1269,44 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="4"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="10"/>
       <c r="G25" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="5"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="4"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="10"/>
       <c r="G26" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="10" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -1261,12 +1314,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
       <c r="G28" s="1" t="s">
         <v>67</v>
       </c>
@@ -1275,103 +1328,233 @@
       <c r="A29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>83</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="C30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D30" s="10" t="s">
+    </row>
+    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G30" s="8" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="E31" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C31" s="6" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="8"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="D31" s="4" t="s">
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="8"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+      <c r="G33" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E31" s="5" t="s">
+    </row>
+    <row r="34" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="5"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="8"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="F35" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="8"/>
+      <c r="B36" s="10"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A38" s="8"/>
+      <c r="B38" s="10"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="8"/>
+      <c r="B39" s="10"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="10"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="10"/>
+      <c r="G39" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="8"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="10"/>
+      <c r="G40" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A41" s="8"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="8"/>
+      <c r="F41" s="10"/>
+      <c r="G41" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
+  <mergeCells count="60">
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
     <mergeCell ref="F24:F26"/>
     <mergeCell ref="F27:F28"/>
     <mergeCell ref="A31:A33"/>
@@ -1380,46 +1563,44 @@
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="F31:F33"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="E4:E8"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="F4:F8"/>
     <mergeCell ref="F9:F12"/>
     <mergeCell ref="F13:F15"/>
     <mergeCell ref="F16:F21"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="E27:E28"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A24:A26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="457" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAB55474-0266-4454-828D-26802BD9B0BC}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DAC169-5DEF-4583-A30C-A98BC6EE9417}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-60" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
   <si>
     <t>Paper</t>
   </si>
@@ -366,12 +366,6 @@
     <t>Environmental thresholds for ambient abiotic conditions</t>
   </si>
   <si>
-    <t>The Rise and Fall of a Reindeer Herd</t>
-  </si>
-  <si>
-    <t>Scheffer</t>
-  </si>
-  <si>
     <t>Rangifer tarandus</t>
   </si>
   <si>
@@ -381,19 +375,51 @@
     <t>2) From behavioral observations and food preference experiments, taller shrub-like lichens are a key winter foods supply for the reindeer, a combination of cold winters that crusted ice inhibiting reindeer to access the lichens and large numbers that depleted the lichens, die offs were seen during the winter.</t>
   </si>
   <si>
-    <t>3) a small lack of sampling, corresponded with a period of military occupation, so poaching could have happened but the decline in popualtion size was already underway.</t>
-  </si>
-  <si>
-    <t>4) Disease and inbreeding were mentioned and ruled out, but with little rationale</t>
-  </si>
-  <si>
-    <t>Extreme Overshoot Of Resource Carrying Capacity</t>
-  </si>
-  <si>
-    <t>Intermediate</t>
-  </si>
-  <si>
-    <t>5) Question was why didn't St. George Island have a similar trend though the islands were of similar size</t>
+    <t>Stong</t>
+  </si>
+  <si>
+    <r>
+      <t>The Rise and Fall of a Reindeer Herd; Climate, snow, ice, crashes, and declines in populations of reindeer and caribou (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Rangifer tarandus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> L.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Scheffer; Tyler</t>
+  </si>
+  <si>
+    <t>Boom-Bust, Overshoot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource depletion </t>
+  </si>
+  <si>
+    <t>3) a small lack of sampling, corresponded with a period of military occupation, so poaching could have happened but the decline in popualtion size was already underway, Harvest was small portion in other locations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4) Natural mortality  was large, and causes of death were deemed starvation, but these were sample relative to the large declines, emigration was responsible for one locaiton but can't be in many of the introduced location which were islands, most often it was young and old that died </t>
+  </si>
+  <si>
+    <t>5) Total snowfall appeared to correlate with declines when presented, but there were counter examples, suggesting that there is a synergy between high numbers and high snow</t>
   </si>
 </sst>
 </file>
@@ -479,13 +505,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -920,16 +946,16 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="11" t="s">
@@ -943,33 +969,33 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
+      <c r="A3" s="9"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="9" t="s">
         <v>78</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -977,66 +1003,66 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
+      <c r="A5" s="9"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
+      <c r="A6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
       <c r="G6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="8"/>
-      <c r="B7" s="10"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
       <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="8"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
       <c r="G8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="8" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -1044,55 +1070,55 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="10"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="8"/>
       <c r="G10" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="10"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="8"/>
       <c r="G11" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="8"/>
       <c r="G12" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="10" t="s">
+      <c r="F13" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="1" t="s">
@@ -1100,44 +1126,44 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="8"/>
       <c r="G14" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="8"/>
       <c r="G15" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="10" t="s">
+      <c r="F16" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G16" s="1" t="s">
@@ -1145,56 +1171,56 @@
       </c>
     </row>
     <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="8"/>
       <c r="G17" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="10"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="8"/>
       <c r="G18" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="10"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="8"/>
       <c r="G19" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="10"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="8"/>
       <c r="G20" s="1" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="8"/>
       <c r="G21" s="1" t="s">
         <v>50</v>
       </c>
@@ -1246,22 +1272,22 @@
       </c>
     </row>
     <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="8" t="s">
+      <c r="E24" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="8" t="s">
         <v>44</v>
       </c>
       <c r="G24" s="1" t="s">
@@ -1269,44 +1295,44 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="10"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="8"/>
       <c r="G25" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="10"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="8"/>
       <c r="G26" s="1" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
+      <c r="A27" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="C27" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="1" t="s">
@@ -1314,12 +1340,12 @@
       </c>
     </row>
     <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
       <c r="G28" s="1" t="s">
         <v>67</v>
       </c>
@@ -1371,22 +1397,22 @@
       </c>
     </row>
     <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F31" s="8" t="s">
+      <c r="F31" s="9" t="s">
         <v>97</v>
       </c>
       <c r="G31" s="1" t="s">
@@ -1394,23 +1420,23 @@
       </c>
     </row>
     <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
       <c r="G32" s="1" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
       <c r="G33" s="1" t="s">
         <v>96</v>
       </c>
@@ -1439,22 +1465,22 @@
       </c>
     </row>
     <row r="35" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="C35" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="8" t="s">
+      <c r="E35" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F35" s="10" t="s">
+      <c r="F35" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="4" t="s">
@@ -1462,90 +1488,124 @@
       </c>
     </row>
     <row r="36" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="8"/>
-      <c r="B36" s="10"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="10"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="10"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="8"/>
       <c r="G36" s="4" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="8" t="s">
+      <c r="A37" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="D37" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E37" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C37" s="9" t="s">
+    </row>
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="9"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="F37" s="10" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="9"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="10"/>
+      <c r="D39" s="8"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G37" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A38" s="8"/>
-      <c r="B38" s="10"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="8"/>
-      <c r="B39" s="10"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="10"/>
-      <c r="G39" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="8"/>
-      <c r="B40" s="10"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="10"/>
+    </row>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="9"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="10"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="8"/>
       <c r="G40" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A41" s="8"/>
-      <c r="B41" s="10"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="10"/>
+        <v>118</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="8"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="8"/>
       <c r="G41" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F21"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="E35:E36"/>
@@ -1562,45 +1622,11 @@
     <mergeCell ref="C31:C33"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{77DAC169-5DEF-4583-A30C-A98BC6EE9417}"/>
+  <xr:revisionPtr revIDLastSave="712" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2152032-4CBD-4712-BE58-043CEFB140DC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
+    <workbookView xWindow="-19320" yWindow="-60" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
-    <sheet name="Mechanism" sheetId="1" r:id="rId2"/>
+    <sheet name="Mechanism_Supplementary" sheetId="1" r:id="rId2"/>
+    <sheet name="Table 1" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="128">
   <si>
     <t>Paper</t>
   </si>
@@ -138,9 +139,6 @@
     <t xml:space="preserve">1) Rock substrate is the preferable shelter from predation and cannabilism for rusty crayfish, but they can use macrophytes as well. </t>
   </si>
   <si>
-    <t>Invasive species unfavorabley alters ecosystem for future generations</t>
-  </si>
-  <si>
     <t>3) Presented data show a strong association between lakes that have declines like these lakes and lakes that had no declines and the prevalence of substrate. This is strong evidence because there was multiple lakes so larger sample size</t>
   </si>
   <si>
@@ -355,9 +353,6 @@
   </si>
   <si>
     <t>Hemichromis letourneuxi</t>
-  </si>
-  <si>
-    <t>1) Cold water and drought events preceeded the boom-bust, and large non-native fishes experienced declines during those cold water conditions</t>
   </si>
   <si>
     <t>2) Paper was more focused on impacts that non-natives have on native species</t>
@@ -421,12 +416,42 @@
   <si>
     <t>5) Total snowfall appeared to correlate with declines when presented, but there were counter examples, suggesting that there is a synergy between high numbers and high snow</t>
   </si>
+  <si>
+    <t>Invasive species unfavorabley alters ecosystem for future generations*</t>
+  </si>
+  <si>
+    <t>Number of Studies</t>
+  </si>
+  <si>
+    <t>Strong</t>
+  </si>
+  <si>
+    <t>Intermediate</t>
+  </si>
+  <si>
+    <t>Environmental Thresholds</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Invasive species unfavorably alter ecosystem for future generations</t>
+  </si>
+  <si>
+    <t>Not Specified</t>
+  </si>
+  <si>
+    <t>1) Cold water and drought events preceeded the boom-bust, and large non-native fishes experienced declines during those cold water conditions and drought conditions</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -442,6 +467,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -451,7 +484,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -479,11 +512,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -504,6 +555,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -513,8 +567,78 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -890,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -898,7 +1022,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -930,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>13</v>
@@ -946,22 +1070,22 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>26</v>
       </c>
       <c r="G2" t="s">
@@ -969,294 +1093,294 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="10"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
+      <c r="A3" s="10"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
       <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9" t="s">
-        <v>78</v>
+      <c r="F4" s="10" t="s">
+        <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="9"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
+      <c r="A5" s="10"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
       <c r="G6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="9"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
+      <c r="A7" s="10"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
       <c r="G7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="9"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
       <c r="G8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>79</v>
+      <c r="E9" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>78</v>
       </c>
       <c r="G9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="9"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9"/>
       <c r="G10" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="1" t="s">
+    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="B13" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="C13" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="10" t="s">
+    </row>
+    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F16" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="10"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="9"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="1" t="s">
+    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="9"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="1" t="s">
+    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="9"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="1" t="s">
+    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="9"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="1" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="1" t="s">
         <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="9"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>52</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>53</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="F22" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="C23" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>14</v>
@@ -1265,347 +1389,313 @@
         <v>27</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="9" t="s">
+      <c r="B24" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="10" t="s">
+    </row>
+    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="D27" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E27" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="1" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="9"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>81</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>82</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>89</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G30" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="9" t="s">
+      <c r="B31" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="8" t="s">
+      <c r="C31" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="D31" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="G31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="10"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+      <c r="G32" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="9"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="1" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="10"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="1" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="9"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="1" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>14</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="9" t="s">
+      <c r="A35" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="B35" s="8" t="s">
+      <c r="C35" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="C35" s="10" t="s">
+      <c r="D35" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="10"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="10"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="9"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="10"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="9"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="4" t="s">
+    </row>
+    <row r="37" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9" t="s">
+      <c r="D37" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="B37" s="8" t="s">
+      <c r="E37" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="F37" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="10"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="D37" s="8" t="s">
+    </row>
+    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="10"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="10"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E37" s="9" t="s">
+    </row>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="10"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="10"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="F37" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="9"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="9"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="9"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="10"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="9"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="1" t="s">
+    </row>
+    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="1" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="9"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="10"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="9"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="10"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="1" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="F16:F21"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="A16:A21"/>
-    <mergeCell ref="B16:B21"/>
-    <mergeCell ref="C16:C21"/>
-    <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="D35:D36"/>
     <mergeCell ref="E35:E36"/>
@@ -1622,11 +1712,348 @@
     <mergeCell ref="C31:C33"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="F31:F33"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="B16:B21"/>
+    <mergeCell ref="C16:C21"/>
+    <mergeCell ref="D16:D21"/>
+    <mergeCell ref="E16:E21"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="F16:F21"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB17AF2-F675-49FF-B120-470F5A4D23AB}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="34.44140625" customWidth="1"/>
+    <col min="2" max="2" width="16" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.21875" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="35" t="s">
+        <v>120</v>
+      </c>
+      <c r="C2" s="36">
+        <v>1</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="29"/>
+      <c r="B3" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="29"/>
+      <c r="B4" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C4" s="23">
+        <v>4</v>
+      </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="29"/>
+      <c r="B5" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="16">
+        <v>1</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="33"/>
+      <c r="B6" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="32">
+        <f>SUM(C2:C5)</f>
+        <v>6</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="13"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="30"/>
+      <c r="B8" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="30"/>
+      <c r="B9" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="30"/>
+      <c r="B10" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="34"/>
+      <c r="B11" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="32">
+        <f>SUM(C7:C10)</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="29"/>
+      <c r="B13" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" s="21">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="29"/>
+      <c r="B14" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="29"/>
+      <c r="B15" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="33"/>
+      <c r="B16" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C16" s="32">
+        <f>SUM(C12:C15)</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="19"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="19"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="29"/>
+      <c r="B18" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>124</v>
+      </c>
+      <c r="D18" s="17"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="29"/>
+      <c r="B19" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="21">
+        <v>4</v>
+      </c>
+      <c r="D19" s="19"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="14"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="29"/>
+      <c r="B20" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="17"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="14"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="33"/>
+      <c r="B21" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="32">
+        <f>SUM(C17:C20)</f>
+        <v>5</v>
+      </c>
+      <c r="D21" s="17"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="28">
+        <v>4</v>
+      </c>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="A7:A11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="712" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B2152032-4CBD-4712-BE58-043CEFB140DC}"/>
+  <xr:revisionPtr revIDLastSave="787" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23097938-25DD-4794-9008-AA236724967F}"/>
   <bookViews>
-    <workbookView xWindow="-19320" yWindow="-60" windowWidth="19440" windowHeight="14880" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
   <si>
     <t>Paper</t>
   </si>
@@ -257,9 +257,6 @@
   </si>
   <si>
     <t>Pseudodiaptomus forbesi</t>
-  </si>
-  <si>
-    <t>multiple</t>
   </si>
   <si>
     <t>Aurelia aurita</t>
@@ -445,6 +442,15 @@
   </si>
   <si>
     <t>1) Cold water and drought events preceeded the boom-bust, and large non-native fishes experienced declines during those cold water conditions and drought conditions</t>
+  </si>
+  <si>
+    <t>Acridotheres tristis; Passer domesticus; Garrulax canorus; Lonchura punctulata; Amandava amandava; Sicalis flaveola; Sturnella neglecta; Crithagra mozambica; Geopelia striata; Spilopelia chinensis; Psittacula krameri; Brotogeris versicolurus</t>
+  </si>
+  <si>
+    <t># of time series</t>
+  </si>
+  <si>
+    <t># of species</t>
   </si>
 </sst>
 </file>
@@ -534,7 +540,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -555,90 +561,77 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -655,10 +648,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -998,7 +987,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -1014,7 +1003,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -1022,7 +1011,7 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -1032,21 +1021,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CF18FAA-193E-4ADD-BAC0-7E416D9C0956}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="18.77734375" customWidth="1"/>
-    <col min="7" max="7" width="67.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="57.77734375" customWidth="1"/>
+    <col min="4" max="6" width="24.109375" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="18.77734375" customWidth="1"/>
+    <col min="9" max="9" width="67.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="57.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1060,296 +1049,362 @@
         <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="30">
+        <v>1</v>
+      </c>
+      <c r="F2" s="30">
+        <v>1</v>
+      </c>
+      <c r="G2" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="H2" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="10"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="1" t="s">
+    <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A3" s="22"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="21"/>
+      <c r="H3" s="21"/>
+      <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="31">
+        <v>1</v>
+      </c>
+      <c r="F4" s="31">
+        <v>1</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="H4" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="22"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="22"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="22"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" s="31">
+        <v>1</v>
+      </c>
+      <c r="F9" s="31">
+        <v>1</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="H9" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="10"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="10"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="11"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="10"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="1" t="s">
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="10"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="1" t="s">
+    <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="22"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="1" t="s">
+    <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="22"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
+    <row r="13" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="23" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="29">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1</v>
+      </c>
+      <c r="G13" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="H13" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="10"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="1" t="s">
+    <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="1" t="s">
+    <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="21"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
+    <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="29">
+        <v>1</v>
+      </c>
+      <c r="F16" s="29">
+        <v>1</v>
+      </c>
+      <c r="G16" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="H16" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="1" t="s">
+    <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="22"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="1" t="s">
+    <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="22"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="1" t="s">
+    <row r="19" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="22"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="1" t="s">
+    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="22"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="1" t="s">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="22"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
@@ -1357,22 +1412,28 @@
         <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>73</v>
+        <v>127</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="8">
+        <v>12</v>
+      </c>
+      <c r="F22" s="8">
+        <v>12</v>
+      </c>
+      <c r="G22" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="H22" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>55</v>
       </c>
@@ -1380,377 +1441,471 @@
         <v>56</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+      <c r="F23" s="8">
+        <v>1</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="H23" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
+    <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="31">
+        <v>9</v>
+      </c>
+      <c r="F24" s="31">
+        <v>1</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="22"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="29">
+        <v>1</v>
+      </c>
+      <c r="F27" s="29">
+        <v>1</v>
+      </c>
+      <c r="G27" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="H27" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="1" t="s">
+    <row r="28" spans="1:9" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="22"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F29" s="6" t="s">
+      <c r="E29" s="8">
+        <v>1</v>
+      </c>
+      <c r="F29" s="8">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E30" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F30" s="6" t="s">
+      <c r="E30" s="8">
+        <v>1</v>
+      </c>
+      <c r="F30" s="8">
+        <v>1</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="I30" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="22" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
+      <c r="B31" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="C31" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="D31" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="29">
+        <v>1</v>
+      </c>
+      <c r="F31" s="29">
+        <v>1</v>
+      </c>
+      <c r="G31" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F31" s="10" t="s">
+    </row>
+    <row r="32" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="22"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="22"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="G31" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="10"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="4" t="s">
+      <c r="C34" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>99</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="8">
+        <v>1</v>
+      </c>
+      <c r="F34" s="8">
+        <v>1</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="22" t="s">
         <v>101</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="B35" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="29">
+        <v>2</v>
+      </c>
+      <c r="F35" s="29">
+        <v>1</v>
+      </c>
+      <c r="G35" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C35" s="11" t="s">
+      <c r="I35" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="22"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="21"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="22"/>
+      <c r="H36" s="21"/>
+      <c r="I36" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="9"/>
-      <c r="G36" s="4" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+    </row>
+    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="9" t="s">
+      <c r="C37" s="23" t="s">
+        <v>106</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="E37" s="29">
+        <v>2</v>
+      </c>
+      <c r="F37" s="29">
+        <v>1</v>
+      </c>
+      <c r="G37" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="E37" s="10" t="s">
+    </row>
+    <row r="38" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="22"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="22"/>
+      <c r="H38" s="21"/>
+      <c r="I38" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="22"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="22"/>
+      <c r="H39" s="21"/>
+      <c r="I39" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="10"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="9"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="1" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="10"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="10"/>
-      <c r="F39" s="9"/>
-      <c r="G39" s="1" t="s">
+    </row>
+    <row r="40" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="22"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="22"/>
+      <c r="H40" s="21"/>
+      <c r="I40" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="10"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="10"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="1" t="s">
+    <row r="41" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="22"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="21"/>
+      <c r="I41" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="10"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="11"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="10"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="D35:D36"/>
+  <mergeCells count="80">
     <mergeCell ref="E35:E36"/>
     <mergeCell ref="F35:F36"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="F24:F26"/>
+    <mergeCell ref="E27:E28"/>
     <mergeCell ref="F27:F28"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="F31:F33"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H8"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="H16:H21"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="H31:H33"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="B16:B21"/>
     <mergeCell ref="C16:C21"/>
     <mergeCell ref="D16:D21"/>
-    <mergeCell ref="E16:E21"/>
-    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="G16:G21"/>
+    <mergeCell ref="G24:G26"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="D27:D28"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="F9:F12"/>
-    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="G27:G28"/>
+    <mergeCell ref="E16:E21"/>
     <mergeCell ref="F16:F21"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="G31:G33"/>
+    <mergeCell ref="H37:H41"/>
+    <mergeCell ref="G37:G41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1762,7 +1917,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -1772,281 +1927,239 @@
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="35" t="s">
+      <c r="C2" s="20">
+        <v>1</v>
+      </c>
+      <c r="D2" s="11"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="22"/>
+      <c r="B3" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C2" s="36">
-        <v>1</v>
-      </c>
-      <c r="D2" s="26"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="13"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="29"/>
-      <c r="B3" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="13"/>
+      <c r="C3" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="29"/>
-      <c r="B4" s="19" t="s">
+      <c r="A4" s="22"/>
+      <c r="B4" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="12">
         <v>4</v>
       </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="13"/>
+      <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="29"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="16">
-        <v>1</v>
-      </c>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="13"/>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="33"/>
-      <c r="B6" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="32">
+      <c r="A6" s="25"/>
+      <c r="B6" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="18">
         <f>SUM(C2:C5)</f>
         <v>6</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="13"/>
+      <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="20" t="s">
+      <c r="A7" s="27" t="s">
+        <v>113</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+      <c r="B8" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="30"/>
-      <c r="B8" s="18" t="s">
+      <c r="C8" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="27"/>
+      <c r="B9" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="27"/>
+      <c r="B10" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="28"/>
+      <c r="B11" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="18">
+        <f>SUM(C7:C10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="22"/>
+      <c r="B13" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="22"/>
+      <c r="B14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="22"/>
+      <c r="B15" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="25"/>
+      <c r="B16" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="18">
+        <f>SUM(C12:C15)</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="8"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="30"/>
-      <c r="B9" s="18" t="s">
+      <c r="B17" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="8"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="22"/>
+      <c r="B18" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="8"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="22"/>
+      <c r="B19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
-      <c r="B10" s="19" t="s">
+      <c r="C19" s="12">
+        <v>4</v>
+      </c>
+      <c r="D19" s="10"/>
+      <c r="E19" s="8"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="22"/>
+      <c r="B20" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="34"/>
-      <c r="B11" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="32">
-        <f>SUM(C7:C10)</f>
-        <v>1</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="29"/>
-      <c r="B13" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C13" s="21">
-        <v>1</v>
-      </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="29"/>
-      <c r="B14" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="29"/>
-      <c r="B15" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="16"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="33"/>
-      <c r="B16" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="32">
-        <f>SUM(C12:C15)</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="19"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="14"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="29" t="s">
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6"/>
+      <c r="E20" s="8"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="25"/>
+      <c r="B21" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="19"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="14"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="29"/>
-      <c r="B18" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="14"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="29"/>
-      <c r="B19" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="21">
-        <v>4</v>
-      </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="14"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="29"/>
-      <c r="B20" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="16">
-        <v>1</v>
-      </c>
-      <c r="D20" s="17"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="14"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="33"/>
-      <c r="B21" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="C21" s="32">
+      <c r="C21" s="18">
         <f>SUM(C17:C20)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="17"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="14"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="B22" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C22" s="28">
+      <c r="D21" s="6"/>
+      <c r="E21" s="8"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="16">
         <v>4</v>
       </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/data/BoomBust_Mechanisms.xlsx
+++ b/data/BoomBust_Mechanisms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f4f5e485ed766aa2/Pictures/Documents/Career/Journal Publications/Manuscripts/Dissertation/boom-bust/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="787" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23097938-25DD-4794-9008-AA236724967F}"/>
+  <xr:revisionPtr revIDLastSave="808" documentId="8_{1B1AAC56-C345-4EC3-95A7-6FD9A5B02C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E360797-FDA0-41B7-B1CA-46B35DD59692}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="14016" windowHeight="12336" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D0698BA0-D8A4-462B-B44D-ABAD27A63A84}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="132">
   <si>
     <t>Paper</t>
   </si>
@@ -290,9 +290,6 @@
   </si>
   <si>
     <t>The paper has strong evidence, empirical work testing hypothesized mechanism is presented or cited and is expreimentally obtained, observational evidence includes models with drivers and response data that were apriori selected,alternative mechanisms have also been evaluated and ruled out, the suggested mechanisms is very likely the mechanism. Evidence can be demographically tied.</t>
-  </si>
-  <si>
-    <t>The paper  has evidence, empirical work testing hypothesized mechanism is presented or cited but is mostely correlary alternative mechanisms have also been evaluated and ruled out, may have some post hoc modelling with suggested mechansims. The mechanism presented is likely. Mechanism is not demographically tied.</t>
   </si>
   <si>
     <t>Boom means bust: interactons between El Nino Southern Oscillation (ENSO), rainfall and the processes threatening mammal species in arid australia</t>
@@ -452,12 +449,21 @@
   <si>
     <t># of species</t>
   </si>
+  <si>
+    <t>Number of Time series</t>
+  </si>
+  <si>
+    <t>Number of Species</t>
+  </si>
+  <si>
+    <t>The paper has evidence, empirical work testing hypothesized mechanism is presented or cited but is mostely correlary alternative mechanisms have also been evaluated and ruled out, may have some post hoc modelling with suggested mechansims. The mechanism presented is likely. Mechanism is not demographically tied.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -481,6 +487,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -490,7 +509,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -536,11 +555,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -568,18 +616,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -601,6 +637,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -610,7 +655,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -618,19 +663,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -648,6 +724,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1003,7 +1083,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
@@ -1026,7 +1106,7 @@
   <cols>
     <col min="1" max="1" width="23.5546875" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" customWidth="1"/>
     <col min="4" max="6" width="24.109375" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
     <col min="8" max="8" width="18.77734375" customWidth="1"/>
@@ -1049,10 +1129,10 @@
         <v>13</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>2</v>
@@ -1065,28 +1145,28 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="30">
-        <v>1</v>
-      </c>
-      <c r="F2" s="30">
-        <v>1</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="E2" s="23">
+        <v>1</v>
+      </c>
+      <c r="F2" s="23">
+        <v>1</v>
+      </c>
+      <c r="G2" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="19" t="s">
         <v>26</v>
       </c>
       <c r="I2" t="s">
@@ -1094,41 +1174,41 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
       <c r="I3" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="C4" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="31">
-        <v>1</v>
-      </c>
-      <c r="F4" s="31">
-        <v>1</v>
-      </c>
-      <c r="G4" s="22" t="s">
+      <c r="E4" s="18">
+        <v>1</v>
+      </c>
+      <c r="F4" s="18">
+        <v>1</v>
+      </c>
+      <c r="G4" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="21" t="s">
         <v>76</v>
       </c>
       <c r="I4" s="1" t="s">
@@ -1136,80 +1216,80 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="22"/>
-      <c r="H5" s="22"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
       <c r="I5" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
       <c r="I6" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="21"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="31"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
       <c r="I7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="21"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
       <c r="I8" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="31">
-        <v>1</v>
-      </c>
-      <c r="F9" s="31">
-        <v>1</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="21" t="s">
+      <c r="E9" s="18">
+        <v>1</v>
+      </c>
+      <c r="F9" s="18">
+        <v>1</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="20" t="s">
         <v>77</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1217,67 +1297,67 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="21"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="21"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="20"/>
       <c r="I10" s="1" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="21"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="21"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="20"/>
       <c r="I11" s="1" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="21"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="20"/>
       <c r="I12" s="1" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="29">
-        <v>1</v>
-      </c>
-      <c r="F13" s="29">
-        <v>1</v>
-      </c>
-      <c r="G13" s="22" t="s">
+      <c r="E13" s="17">
+        <v>1</v>
+      </c>
+      <c r="F13" s="17">
+        <v>1</v>
+      </c>
+      <c r="G13" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="20" t="s">
         <v>43</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1285,54 +1365,54 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="21"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="20"/>
       <c r="I14" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="21"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="20"/>
       <c r="I15" s="1" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="29">
-        <v>1</v>
-      </c>
-      <c r="F16" s="29">
-        <v>1</v>
-      </c>
-      <c r="G16" s="22" t="s">
+      <c r="E16" s="17">
+        <v>1</v>
+      </c>
+      <c r="F16" s="17">
+        <v>1</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="20" t="s">
         <v>43</v>
       </c>
       <c r="I16" s="1" t="s">
@@ -1340,79 +1420,79 @@
       </c>
     </row>
     <row r="17" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="21"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="21"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="21"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="20"/>
       <c r="I17" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="21"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="21"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="20"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="20"/>
       <c r="I18" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="21"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="21"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="20"/>
       <c r="I19" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="21"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="21"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="1" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="22"/>
-      <c r="B21" s="21"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="21"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="20"/>
       <c r="I21" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>127</v>
+      <c r="C22" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>52</v>
@@ -1463,28 +1543,28 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="18">
         <v>9</v>
       </c>
-      <c r="F24" s="31">
-        <v>1</v>
-      </c>
-      <c r="G24" s="22" t="s">
+      <c r="F24" s="18">
+        <v>1</v>
+      </c>
+      <c r="G24" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="H24" s="21" t="s">
+      <c r="H24" s="20" t="s">
         <v>43</v>
       </c>
       <c r="I24" s="1" t="s">
@@ -1492,54 +1572,54 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="21"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="18"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="1" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="21"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="18"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="1" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="22" t="s">
+      <c r="A27" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="29">
-        <v>1</v>
-      </c>
-      <c r="F27" s="29">
-        <v>1</v>
-      </c>
-      <c r="G27" s="21" t="s">
+      <c r="E27" s="17">
+        <v>1</v>
+      </c>
+      <c r="F27" s="17">
+        <v>1</v>
+      </c>
+      <c r="G27" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H27" s="21" t="s">
+      <c r="H27" s="20" t="s">
         <v>26</v>
       </c>
       <c r="I27" s="1" t="s">
@@ -1547,14 +1627,14 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
+      <c r="A28" s="21"/>
+      <c r="B28" s="20"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
       <c r="I28" s="1" t="s">
         <v>66</v>
       </c>
@@ -1579,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>43</v>
@@ -1590,13 +1670,13 @@
     </row>
     <row r="30" spans="1:9" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>14</v>
@@ -1608,79 +1688,79 @@
         <v>1</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>43</v>
       </c>
       <c r="I30" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="22" t="s">
+      <c r="B31" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="C31" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="D31" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="17">
+        <v>1</v>
+      </c>
+      <c r="F31" s="17">
+        <v>1</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I31" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="29">
-        <v>1</v>
-      </c>
-      <c r="F31" s="29">
-        <v>1</v>
-      </c>
-      <c r="G31" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>95</v>
-      </c>
-      <c r="I31" s="1" t="s">
+    </row>
+    <row r="32" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="21"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="20"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="21"/>
-      <c r="C32" s="23"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="1" t="s">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="21"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="1" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A33" s="22"/>
-      <c r="B33" s="21"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>14</v>
@@ -1692,183 +1772,161 @@
         <v>1</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>26</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="22" t="s">
+      <c r="A35" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="B35" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="C35" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C35" s="23" t="s">
+      <c r="D35" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="17">
+        <v>2</v>
+      </c>
+      <c r="F35" s="17">
+        <v>1</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21"/>
+      <c r="B36" s="20"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="21"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D35" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="E35" s="29">
+    </row>
+    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="17">
         <v>2</v>
       </c>
-      <c r="F35" s="29">
-        <v>1</v>
-      </c>
-      <c r="G35" s="22" t="s">
-        <v>19</v>
-      </c>
-      <c r="H35" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
-      <c r="B36" s="21"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="21"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="21"/>
-      <c r="I36" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C37" s="23" t="s">
+      <c r="F37" s="17">
+        <v>1</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="H37" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="D37" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="E37" s="29">
-        <v>2</v>
-      </c>
-      <c r="F37" s="29">
-        <v>1</v>
-      </c>
-      <c r="G37" s="22" t="s">
+    </row>
+    <row r="38" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="21"/>
+      <c r="B38" s="20"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="17"/>
+      <c r="F38" s="17"/>
+      <c r="G38" s="21"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="21"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="21"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="H37" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="22"/>
-      <c r="B38" s="21"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="21"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="22"/>
-      <c r="H38" s="21"/>
-      <c r="I38" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
-      <c r="B39" s="21"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="21"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="21"/>
-      <c r="I39" s="1" t="s">
+    </row>
+    <row r="40" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="21"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="21"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
-      <c r="B40" s="21"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="22"/>
-      <c r="H40" s="21"/>
-      <c r="I40" s="1" t="s">
+    <row r="41" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="21"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="21"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="1" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="22"/>
-      <c r="B41" s="21"/>
-      <c r="C41" s="23"/>
-      <c r="D41" s="21"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="E35:E36"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="E37:E41"/>
-    <mergeCell ref="F37:F41"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="F31:F33"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="H4:H8"/>
-    <mergeCell ref="H9:H12"/>
-    <mergeCell ref="H13:H15"/>
-    <mergeCell ref="H16:H21"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="C4:C8"/>
-    <mergeCell ref="D4:D8"/>
-    <mergeCell ref="G4:G8"/>
-    <mergeCell ref="E4:E8"/>
-    <mergeCell ref="F4:F8"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="G13:G15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="F13:F15"/>
-    <mergeCell ref="G9:G12"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="C9:C12"/>
-    <mergeCell ref="B9:B12"/>
-    <mergeCell ref="A9:A12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="H37:H41"/>
+    <mergeCell ref="G37:G41"/>
+    <mergeCell ref="D37:D41"/>
+    <mergeCell ref="C37:C41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="G35:G36"/>
+    <mergeCell ref="H35:H36"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="C35:C36"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="H27:H28"/>
+    <mergeCell ref="A31:A33"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="G31:G33"/>
     <mergeCell ref="H31:H33"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="B16:B21"/>
@@ -1885,27 +1943,49 @@
     <mergeCell ref="G27:G28"/>
     <mergeCell ref="E16:E21"/>
     <mergeCell ref="F16:F21"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="G35:G36"/>
-    <mergeCell ref="H35:H36"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:C36"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="H27:H28"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="G31:G33"/>
-    <mergeCell ref="H37:H41"/>
-    <mergeCell ref="G37:G41"/>
-    <mergeCell ref="D37:D41"/>
-    <mergeCell ref="C37:C41"/>
-    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="G9:G12"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="C9:C12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F9:F12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="G13:G15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="F13:F15"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="A4:A8"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="C4:C8"/>
+    <mergeCell ref="D4:D8"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="H4:H8"/>
+    <mergeCell ref="H9:H12"/>
+    <mergeCell ref="H13:H15"/>
+    <mergeCell ref="H16:H21"/>
+    <mergeCell ref="E35:E36"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="E37:E41"/>
+    <mergeCell ref="F37:F41"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="F31:F33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1917,248 +1997,364 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.44140625" customWidth="1"/>
-    <col min="2" max="2" width="16" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.21875" customWidth="1"/>
     <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="16">
+        <v>1</v>
+      </c>
+      <c r="D2" s="37">
+        <v>1</v>
+      </c>
+      <c r="E2" s="37">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C2" s="20">
-        <v>1</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>123</v>
+      <c r="C3" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E3" s="30" t="s">
+        <v>122</v>
       </c>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="29">
         <v>4</v>
       </c>
+      <c r="D4" s="30">
+        <v>12</v>
+      </c>
+      <c r="E4" s="30">
+        <v>4</v>
+      </c>
       <c r="F4" s="4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="10" t="s">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="31">
+        <v>1</v>
+      </c>
+      <c r="D5" s="30">
+        <v>2</v>
+      </c>
+      <c r="E5" s="30">
         <v>1</v>
       </c>
       <c r="F5" s="4"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="18">
+      <c r="A6" s="24"/>
+      <c r="B6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="14">
         <f>SUM(C2:C5)</f>
         <v>6</v>
       </c>
+      <c r="D6" s="38">
+        <v>15</v>
+      </c>
+      <c r="E6" s="39">
+        <v>6</v>
+      </c>
       <c r="F6" s="4"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="11" t="s">
+      <c r="A7" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="31">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30">
+        <v>2</v>
+      </c>
+      <c r="E7" s="40">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="32"/>
+      <c r="B8" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="10" t="s">
+      <c r="C8" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="32"/>
+      <c r="B9" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="4"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="32"/>
+      <c r="B10" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="14">
+        <f>SUM(C7:C10)</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="39">
+        <v>2</v>
+      </c>
+      <c r="E11" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="29">
+        <v>1</v>
+      </c>
+      <c r="D13" s="30">
+        <v>1</v>
+      </c>
+      <c r="E13" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="24"/>
+      <c r="B16" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="14">
+        <f>SUM(C12:C15)</f>
+        <v>1</v>
+      </c>
+      <c r="D16" s="39">
+        <v>1</v>
+      </c>
+      <c r="E16" s="39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="27" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="27"/>
-      <c r="B9" s="10" t="s">
+      <c r="B17" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D18" s="30" t="s">
+        <v>122</v>
+      </c>
+      <c r="E18" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="27"/>
-      <c r="B10" s="10" t="s">
+      <c r="C19" s="29">
+        <v>4</v>
+      </c>
+      <c r="D19" s="30">
+        <v>2</v>
+      </c>
+      <c r="E19" s="30">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="18">
-        <f>SUM(C7:C10)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
-      <c r="B16" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="18">
-        <f>SUM(C12:C15)</f>
-        <v>1</v>
-      </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="8"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="C20" s="31">
+        <v>1</v>
+      </c>
+      <c r="D20" s="30">
+        <v>1</v>
+      </c>
+      <c r="E20" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="24"/>
+      <c r="B21" s="13" t="s">
         <v>121</v>
       </c>
-      <c r="B17" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="8"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="8"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="12">
-        <v>4</v>
-      </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
-      <c r="B20" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6"/>
-      <c r="E20" s="8"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="18">
+      <c r="C21" s="14">
         <f>SUM(C17:C20)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="6"/>
-      <c r="E21" s="8"/>
+      <c r="D21" s="39">
+        <v>3</v>
+      </c>
+      <c r="E21" s="38">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C22" s="16">
+        <v>124</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="C22" s="12">
         <v>4</v>
+      </c>
+      <c r="D22" s="41">
+        <v>15</v>
+      </c>
+      <c r="E22" s="34">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
